--- a/teste.xlsx
+++ b/teste.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Descricao_Limpa</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>0.11cmX0.50cm BRANCO</t>
-  </si>
-  <si>
-    <t>3/4"X1/2" nan</t>
   </si>
 </sst>
 </file>
@@ -503,7 +500,7 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
